--- a/templates/yuridik_shablon.xlsx
+++ b/templates/yuridik_shablon.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Шаблон" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаблон" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
@@ -444,62 +444,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Компания-получатель</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ФИО получателя</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Адрес получателя</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Телефон получателя</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Шифр клиента</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Масса посылки</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Поручение</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Количество мест</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Режим</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Город-получатель</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Оплата получателем</t>
         </is>
